--- a/artfynd/S 917-2023 artfynd.xlsx
+++ b/artfynd/S 917-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1773,10 +1773,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>102386652</v>
+        <v>135422119</v>
       </c>
       <c r="B11" t="n">
-        <v>56876</v>
+        <v>58462</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1784,21 +1784,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>208257</v>
+        <v>100058</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Mindre flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Ficedula parva</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1806,36 +1806,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tattby NR, Srm</t>
+          <t>Erstavik, Nacka, Erstavikskvarn, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686746</v>
+        <v>686730</v>
       </c>
       <c r="R11" t="n">
-        <v>6574817</v>
+        <v>6574772</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1854,32 +1837,32 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Boo</t>
+          <t>Nacka</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-05-19</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På stigen från Erstaviksbadets P til Erstaviks kvarn.</t>
+          <t>Kämpade med en larv i 10 min. Kanske var det föda åt ungar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,56 +1871,55 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Nils MAGNUS Fredriksson</t>
+          <t>Harry  Brar</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Nils MAGNUS Fredriksson</t>
+          <t>Harry  Brar</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/102386652</t>
+          <t>https://artportalen.se/Sighting/135422119</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>83441627</v>
+        <v>102386652</v>
       </c>
       <c r="B12" t="n">
-        <v>106813</v>
+        <v>56876</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>208257</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1945,19 +1927,36 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>3330, 30004834, Srm</t>
+          <t>Tattby NR, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686772</v>
+        <v>686746</v>
       </c>
       <c r="R12" t="n">
-        <v>6574709</v>
+        <v>6574817</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1979,19 +1978,29 @@
           <t>Boo</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>6F91C6BE-D1C6-4B50-AAD8-B5EA7706D625</t>
-        </is>
-      </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2009-05-02</t>
+          <t>2022-05-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På stigen från Erstaviksbadets P til Erstaviks kvarn.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2000,34 +2009,31 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
+          <t>Nils MAGNUS Fredriksson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Miguel Jaramillo</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Trädportalen</t>
-        </is>
-      </c>
+          <t>Nils MAGNUS Fredriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/83441627</t>
+          <t>https://artportalen.se/Sighting/102386652</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>110544707</v>
+        <v>83441627</v>
       </c>
       <c r="B13" t="n">
         <v>106813</v>
@@ -2062,17 +2068,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Nacka kommun, Srm</t>
+          <t>3330, 30004834, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686771</v>
+        <v>686772</v>
       </c>
       <c r="R13" t="n">
         <v>6574709</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,22 +2102,17 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>b13704de-3977-4f20-b2b9-960b0f8849e4</t>
+          <t>6F91C6BE-D1C6-4B50-AAD8-B5EA7706D625</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Stamkvistning.</t>
+          <t>2009-05-02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2126,20 +2127,140 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Miguel Jaramillo</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/83441627</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110544707</v>
+      </c>
+      <c r="B14" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Nacka kommun, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>686771</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6574709</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nacka</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Boo</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>b13704de-3977-4f20-b2b9-960b0f8849e4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-04-28</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Stamkvistning.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
           <t>Julia Stigenberg</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
+      <c r="AX14" t="inlineStr">
         <is>
           <t>Miguel Jaramillo</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
+      <c r="AZ14" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/110544707</t>
         </is>
@@ -2159,6 +2280,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 917-2023 artfynd.xlsx
+++ b/artfynd/S 917-2023 artfynd.xlsx
@@ -1776,7 +1776,7 @@
         <v>135422119</v>
       </c>
       <c r="B11" t="n">
-        <v>58462</v>
+        <v>58464</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
